--- a/tools/importer/reports/import-placeholder-landing.report.xlsx
+++ b/tools/importer/reports/import-placeholder-landing.report.xlsx
@@ -52,7 +52,7 @@
     <t>placeholder-landing</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:53.552Z</t>
+    <t>2026-05-12T08:30:55.933Z</t>
   </si>
   <si>
     <t>Français</t>
@@ -67,7 +67,7 @@
     <t>ch/de</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:59.104Z</t>
+    <t>2026-05-12T08:31:01.401Z</t>
   </si>
   <si>
     <t>Deutsch</t>
@@ -82,7 +82,7 @@
     <t>ch/fr</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:03.699Z</t>
+    <t>2026-05-12T08:31:07.621Z</t>
   </si>
   <si>
     <t>https://wknd.site/ch/fr.html</t>
@@ -94,7 +94,7 @@
     <t>ch/it</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:08.118Z</t>
+    <t>2026-05-12T08:31:12.679Z</t>
   </si>
   <si>
     <t>Italiano</t>
@@ -109,7 +109,7 @@
     <t>de/de</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:12.992Z</t>
+    <t>2026-05-12T08:31:18.182Z</t>
   </si>
   <si>
     <t>https://wknd.site/de/de.html</t>
@@ -121,7 +121,7 @@
     <t>es/es</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:24.853Z</t>
+    <t>2026-05-12T08:31:29.979Z</t>
   </si>
   <si>
     <t>Español</t>
@@ -136,7 +136,7 @@
     <t>fr/fr</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:18.347Z</t>
+    <t>2026-05-12T08:31:23.936Z</t>
   </si>
   <si>
     <t>https://wknd.site/fr/fr.html</t>
@@ -148,7 +148,7 @@
     <t>it/it</t>
   </si>
   <si>
-    <t>2026-05-09T03:04:30.099Z</t>
+    <t>2026-05-12T08:31:36.553Z</t>
   </si>
   <si>
     <t>https://wknd.site/it/it.html</t>
@@ -181,7 +181,7 @@
     <t>us/es</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:48.552Z</t>
+    <t>2026-05-12T08:30:51.183Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/es.html</t>
@@ -196,7 +196,7 @@
     <t>about-page</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:02.569Z</t>
+    <t>2026-05-12T08:30:46.010Z</t>
   </si>
   <si>
     <t>About Us</t>
@@ -214,7 +214,7 @@
     <t>adventures-listing</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:13.777Z</t>
+    <t>2026-05-12T08:27:34.933Z</t>
   </si>
   <si>
     <t>Adventures</t>
@@ -232,7 +232,7 @@
     <t>faqs-page</t>
   </si>
   <si>
-    <t>2026-05-09T02:58:51.957Z</t>
+    <t>2026-05-12T08:30:35.610Z</t>
   </si>
   <si>
     <t>FAQs</t>
@@ -250,7 +250,7 @@
     <t>magazine-listing</t>
   </si>
   <si>
-    <t>2026-05-09T02:58:40.564Z</t>
+    <t>2026-05-12T08:26:26.201Z</t>
   </si>
   <si>
     <t>Magazine</t>
@@ -265,7 +265,7 @@
     <t>us/en/about-us</t>
   </si>
   <si>
-    <t>2026-05-09T02:58:56.516Z</t>
+    <t>2026-05-12T08:30:41.600Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/about-us.html</t>
@@ -277,7 +277,7 @@
     <t>us/en/adventures</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:08.071Z</t>
+    <t>2026-05-12T08:27:28.451Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures.html</t>
@@ -289,7 +289,7 @@
     <t>us/en/faqs</t>
   </si>
   <si>
-    <t>2026-05-09T02:58:45.242Z</t>
+    <t>2026-05-12T08:30:29.662Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/faqs.html</t>
@@ -301,7 +301,7 @@
     <t>us/en/magazine</t>
   </si>
   <si>
-    <t>2026-05-09T02:58:35.327Z</t>
+    <t>2026-05-12T08:26:21.850Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine.html</t>
@@ -316,7 +316,7 @@
     <t>adventure-detail</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:10.303Z</t>
+    <t>2026-05-12T08:29:05.780Z</t>
   </si>
   <si>
     <t>Bali Surf Camp</t>
@@ -331,7 +331,7 @@
     <t>ca/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:15.224Z</t>
+    <t>2026-05-12T08:29:10.402Z</t>
   </si>
   <si>
     <t>Beervana in Portland</t>
@@ -346,7 +346,7 @@
     <t>ca/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:20.498Z</t>
+    <t>2026-05-12T08:29:16.489Z</t>
   </si>
   <si>
     <t>Climbing New Zealand</t>
@@ -361,7 +361,7 @@
     <t>ca/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:25.079Z</t>
+    <t>2026-05-12T08:29:20.705Z</t>
   </si>
   <si>
     <t>Colorado Rock Climbing</t>
@@ -376,7 +376,7 @@
     <t>ca/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:31.169Z</t>
+    <t>2026-05-12T08:29:25.336Z</t>
   </si>
   <si>
     <t>Cycling Southern Utah</t>
@@ -391,7 +391,7 @@
     <t>ca/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:36.270Z</t>
+    <t>2026-05-12T08:29:31.049Z</t>
   </si>
   <si>
     <t>Cycling Tuscany</t>
@@ -406,7 +406,7 @@
     <t>ca/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:42.218Z</t>
+    <t>2026-05-12T08:29:37.050Z</t>
   </si>
   <si>
     <t>Downhill Skiing Wyoming</t>
@@ -421,7 +421,7 @@
     <t>ca/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:47.656Z</t>
+    <t>2026-05-12T08:29:42.847Z</t>
   </si>
   <si>
     <t>Gastronomic Marais Tour</t>
@@ -436,7 +436,7 @@
     <t>ca/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:53.706Z</t>
+    <t>2026-05-12T08:29:47.536Z</t>
   </si>
   <si>
     <t>Napa Wine Tasting</t>
@@ -451,7 +451,7 @@
     <t>ca/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:58.293Z</t>
+    <t>2026-05-12T08:29:53.819Z</t>
   </si>
   <si>
     <t>Riverside Camping</t>
@@ -466,7 +466,7 @@
     <t>ca/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:03.627Z</t>
+    <t>2026-05-12T08:29:58.572Z</t>
   </si>
   <si>
     <t>Ski Touring Mont Blanc</t>
@@ -481,7 +481,7 @@
     <t>ca/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:09.935Z</t>
+    <t>2026-05-12T08:30:02.885Z</t>
   </si>
   <si>
     <t>Surf Camp in Costa Rica</t>
@@ -496,7 +496,7 @@
     <t>ca/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:16.411Z</t>
+    <t>2026-05-12T08:30:08.183Z</t>
   </si>
   <si>
     <t>Tahoe Skiing</t>
@@ -511,7 +511,7 @@
     <t>ca/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:22.426Z</t>
+    <t>2026-05-12T08:30:13.112Z</t>
   </si>
   <si>
     <t>West Coast Cycling</t>
@@ -526,7 +526,7 @@
     <t>ca/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:28.170Z</t>
+    <t>2026-05-12T08:30:18.477Z</t>
   </si>
   <si>
     <t>Whistler Mountain Biking</t>
@@ -541,7 +541,7 @@
     <t>ca/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-05-09T03:03:32.737Z</t>
+    <t>2026-05-12T08:30:24.486Z</t>
   </si>
   <si>
     <t>Yosemite Backpacking</t>
@@ -559,7 +559,7 @@
     <t>magazine-article</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:23.521Z</t>
+    <t>2026-05-12T08:27:22.270Z</t>
   </si>
   <si>
     <t>Arctic Surfing</t>
@@ -574,7 +574,7 @@
     <t>ca/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:12.773Z</t>
+    <t>2026-05-12T08:27:10.525Z</t>
   </si>
   <si>
     <t>Ultimate Guide to LA Skateparks</t>
@@ -589,7 +589,7 @@
     <t>ca/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:01.542Z</t>
+    <t>2026-05-12T08:26:58.655Z</t>
   </si>
   <si>
     <t>San Diego Surf Spots</t>
@@ -604,7 +604,7 @@
     <t>ca/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:19.553Z</t>
+    <t>2026-05-12T08:27:15.815Z</t>
   </si>
   <si>
     <t>Ski Touring</t>
@@ -619,7 +619,7 @@
     <t>ca/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:07.200Z</t>
+    <t>2026-05-12T08:27:04.215Z</t>
   </si>
   <si>
     <t>Western Australia</t>
@@ -634,7 +634,7 @@
     <t>us/en/adventures/bali-surf-camp</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:45.290Z</t>
+    <t>2026-05-12T08:27:40.455Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/bali-surf-camp.html</t>
@@ -646,7 +646,7 @@
     <t>us/en/adventures/beervana-portland</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:49.775Z</t>
+    <t>2026-05-12T08:27:46.011Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/beervana-portland.html</t>
@@ -658,7 +658,7 @@
     <t>us/en/adventures/climbing-new-zealand</t>
   </si>
   <si>
-    <t>2026-05-09T03:00:54.527Z</t>
+    <t>2026-05-12T08:27:51.573Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/climbing-new-zealand.html</t>
@@ -670,7 +670,7 @@
     <t>us/en/adventures/colorado-rock-climbing</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:00.601Z</t>
+    <t>2026-05-12T08:27:56.809Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/colorado-rock-climbing.html</t>
@@ -682,7 +682,7 @@
     <t>us/en/adventures/cycling-southern-utah</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:05.777Z</t>
+    <t>2026-05-12T08:28:00.613Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/cycling-southern-utah.html</t>
@@ -694,7 +694,7 @@
     <t>us/en/adventures/cycling-tuscany</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:11.119Z</t>
+    <t>2026-05-12T08:28:07.293Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/cycling-tuscany.html</t>
@@ -706,7 +706,7 @@
     <t>us/en/adventures/downhill-skiing-wyoming</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:16.595Z</t>
+    <t>2026-05-12T08:28:14.132Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/downhill-skiing-wyoming.html</t>
@@ -718,7 +718,7 @@
     <t>us/en/adventures/gastronomic-marais-tour</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:23.104Z</t>
+    <t>2026-05-12T08:28:18.164Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/gastronomic-marais-tour.html</t>
@@ -730,7 +730,7 @@
     <t>us/en/adventures/napa-wine-tasting</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:29.250Z</t>
+    <t>2026-05-12T08:28:24.242Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/napa-wine-tasting.html</t>
@@ -742,7 +742,7 @@
     <t>us/en/adventures/riverside-camping-australia</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:35.034Z</t>
+    <t>2026-05-12T08:28:29.904Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/riverside-camping-australia.html</t>
@@ -754,7 +754,7 @@
     <t>us/en/adventures/ski-touring-mont-blanc</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:39.624Z</t>
+    <t>2026-05-12T08:28:34.429Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/ski-touring-mont-blanc.html</t>
@@ -766,7 +766,7 @@
     <t>us/en/adventures/surf-camp-costa-rica</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:45.060Z</t>
+    <t>2026-05-12T08:28:39.521Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/surf-camp-costa-rica.html</t>
@@ -778,7 +778,7 @@
     <t>us/en/adventures/tahoe-skiing</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:49.659Z</t>
+    <t>2026-05-12T08:28:44.918Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/tahoe-skiing.html</t>
@@ -790,7 +790,7 @@
     <t>us/en/adventures/west-coast-cycling</t>
   </si>
   <si>
-    <t>2026-05-09T03:01:55.183Z</t>
+    <t>2026-05-12T08:28:49.480Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/west-coast-cycling.html</t>
@@ -802,7 +802,7 @@
     <t>us/en/adventures/whistler-mountain-biking</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:00.520Z</t>
+    <t>2026-05-12T08:28:55.087Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/whistler-mountain-biking.html</t>
@@ -814,7 +814,7 @@
     <t>us/en/adventures/yosemite-backpacking</t>
   </si>
   <si>
-    <t>2026-05-09T03:02:06.158Z</t>
+    <t>2026-05-12T08:29:00.223Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/adventures/yosemite-backpacking.html</t>
@@ -826,7 +826,7 @@
     <t>us/en/magazine/arctic-surfing</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:57.427Z</t>
+    <t>2026-05-12T08:26:52.737Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/arctic-surfing.html</t>
@@ -838,7 +838,7 @@
     <t>us/en/magazine/guide-la-skateparks</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:45.836Z</t>
+    <t>2026-05-12T08:26:42.989Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/guide-la-skateparks.html</t>
@@ -850,7 +850,7 @@
     <t>us/en/magazine/san-diego-surf</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:34.579Z</t>
+    <t>2026-05-12T08:26:31.531Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/san-diego-surf.html</t>
@@ -862,7 +862,7 @@
     <t>us/en/magazine/ski-touring</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:52.435Z</t>
+    <t>2026-05-12T08:26:47.622Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/ski-touring.html</t>
@@ -874,7 +874,7 @@
     <t>us/en/magazine/western-australia</t>
   </si>
   <si>
-    <t>2026-05-09T02:59:39.489Z</t>
+    <t>2026-05-12T08:26:37.484Z</t>
   </si>
   <si>
     <t>https://wknd.site/us/en/magazine/western-australia.html</t>
